--- a/static/data/exports/Retro_DL_AE_2025.xlsx
+++ b/static/data/exports/Retro_DL_AE_2025.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15318,7 +15318,7 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -16055,7 +16055,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -16205,7 +16205,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O230" t="inlineStr">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
@@ -18928,7 +18928,7 @@
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
@@ -19003,7 +19003,7 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -20477,7 +20477,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -20839,7 +20839,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -20914,7 +20914,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O279" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -21139,7 +21139,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -21801,7 +21801,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -21951,7 +21951,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -22026,7 +22026,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -22238,7 +22238,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -23200,7 +23200,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -23350,7 +23350,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -23575,7 +23575,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -23725,7 +23725,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -23800,7 +23800,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -23875,7 +23875,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -24237,7 +24237,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -24312,7 +24312,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -24387,7 +24387,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -24462,7 +24462,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -24687,7 +24687,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -24762,7 +24762,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -25261,7 +25261,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -25486,7 +25486,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -25636,7 +25636,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -25998,7 +25998,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -26073,7 +26073,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -26148,7 +26148,7 @@
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
@@ -26223,7 +26223,7 @@
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
@@ -26298,7 +26298,7 @@
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
@@ -26448,7 +26448,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -26598,7 +26598,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -26885,7 +26885,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -27035,7 +27035,7 @@
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O361" t="inlineStr">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O362" t="inlineStr">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -27260,7 +27260,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
@@ -27485,7 +27485,7 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O367" t="inlineStr">
@@ -27560,7 +27560,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -27635,7 +27635,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -27710,7 +27710,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -27922,7 +27922,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -28072,7 +28072,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -28222,7 +28222,7 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O377" t="inlineStr">
@@ -28297,7 +28297,7 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O378" t="inlineStr">
@@ -28372,7 +28372,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -28447,7 +28447,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -28659,7 +28659,7 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O383" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O384" t="inlineStr">
@@ -28809,7 +28809,7 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O385" t="inlineStr">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -28959,7 +28959,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -29109,7 +29109,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -29334,7 +29334,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -29409,7 +29409,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O395" t="inlineStr">
@@ -29621,7 +29621,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -29771,7 +29771,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -29846,7 +29846,7 @@
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O399" t="inlineStr">
@@ -29921,7 +29921,7 @@
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O400" t="inlineStr">
@@ -29996,7 +29996,7 @@
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O401" t="inlineStr">
@@ -30208,7 +30208,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -30433,7 +30433,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -30583,7 +30583,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -30720,7 +30720,7 @@
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O411" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -30945,7 +30945,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -31020,7 +31020,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -31095,7 +31095,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O417" t="inlineStr">
@@ -31382,7 +31382,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -31532,7 +31532,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
@@ -31607,7 +31607,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -31757,7 +31757,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -31832,7 +31832,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -31982,7 +31982,7 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O428" t="inlineStr">
@@ -32057,7 +32057,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -32132,7 +32132,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -32207,7 +32207,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -32282,7 +32282,7 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O432" t="inlineStr">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O433" t="inlineStr">
@@ -32432,7 +32432,7 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O434" t="inlineStr">
@@ -32460,20 +32460,20 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1505699</v>
+        <v>1505698</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Nitya Nand Singh</t>
+          <t>Mukesh Jain</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>RSHTMNVP</t>
+          <t>RSTJLKPS</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>16502</v>
+        <v>16470</v>
       </c>
       <c r="E435" t="n">
         <v>8</v>
@@ -32497,17 +32497,17 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>Nitya Nand Singh</t>
+          <t>Mukesh Jain</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>RSHTMNVP</t>
+          <t>RSTJLKPS</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -32516,7 +32516,7 @@
         </is>
       </c>
       <c r="P435" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Q435" t="b">
         <v>0</v>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -32610,20 +32610,20 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>1505698</v>
+        <v>1505699</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Mukesh Jain</t>
+          <t>Nitya Nand Singh</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>RSTJLKPS</t>
+          <t>RSHTMNVP</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>16470</v>
+        <v>16502</v>
       </c>
       <c r="E437" t="n">
         <v>8</v>
@@ -32647,17 +32647,17 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>Mukesh Jain</t>
+          <t>Nitya Nand Singh</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>RSTJLKPS</t>
+          <t>RSHTMNVP</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -32666,7 +32666,7 @@
         </is>
       </c>
       <c r="P437" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="Q437" t="b">
         <v>0</v>
@@ -32807,7 +32807,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -32882,7 +32882,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -32957,7 +32957,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -33094,7 +33094,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O443" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O444" t="inlineStr">
@@ -33244,7 +33244,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -33319,7 +33319,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -33469,7 +33469,7 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O448" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O449" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O450" t="inlineStr">
@@ -33694,7 +33694,7 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O451" t="inlineStr">
@@ -33831,7 +33831,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -34056,7 +34056,7 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O456" t="inlineStr">
@@ -34131,7 +34131,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -34268,7 +34268,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O460" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O461" t="inlineStr">
@@ -34493,7 +34493,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -34568,7 +34568,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -34718,7 +34718,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -35005,7 +35005,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -35080,7 +35080,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -35155,7 +35155,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -35230,7 +35230,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -35305,7 +35305,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -35455,7 +35455,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -35530,7 +35530,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -35605,7 +35605,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -35680,7 +35680,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -35755,7 +35755,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -35830,7 +35830,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -36042,7 +36042,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -36117,7 +36117,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -36192,7 +36192,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -36267,7 +36267,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -36342,7 +36342,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -36629,7 +36629,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -36854,7 +36854,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -36929,7 +36929,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -37004,7 +37004,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
@@ -37079,7 +37079,7 @@
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O497" t="inlineStr">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="N516" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O516" t="inlineStr">
@@ -38553,7 +38553,7 @@
       </c>
       <c r="N517" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O517" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="N518" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O518" t="inlineStr">
@@ -38703,7 +38703,7 @@
       </c>
       <c r="N519" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O519" t="inlineStr">
@@ -38840,7 +38840,7 @@
       </c>
       <c r="N521" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O521" t="inlineStr">
@@ -38915,7 +38915,7 @@
       </c>
       <c r="N522" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O522" t="inlineStr">
@@ -38990,7 +38990,7 @@
       </c>
       <c r="N523" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O523" t="inlineStr">
@@ -39065,7 +39065,7 @@
       </c>
       <c r="N524" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O524" t="inlineStr">
@@ -39140,7 +39140,7 @@
       </c>
       <c r="N525" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O525" t="inlineStr">
@@ -39215,7 +39215,7 @@
       </c>
       <c r="N526" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O526" t="inlineStr">
@@ -39290,7 +39290,7 @@
       </c>
       <c r="N527" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O527" t="inlineStr">
@@ -39365,7 +39365,7 @@
       </c>
       <c r="N528" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O528" t="inlineStr">
@@ -39440,7 +39440,7 @@
       </c>
       <c r="N529" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O529" t="inlineStr">
@@ -39515,7 +39515,7 @@
       </c>
       <c r="N530" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O530" t="inlineStr">
@@ -39652,7 +39652,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
@@ -39727,7 +39727,7 @@
       </c>
       <c r="N533" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O533" t="inlineStr">
@@ -39802,7 +39802,7 @@
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -39877,7 +39877,7 @@
       </c>
       <c r="N535" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O535" t="inlineStr">
@@ -39952,7 +39952,7 @@
       </c>
       <c r="N536" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O536" t="inlineStr">
@@ -40027,7 +40027,7 @@
       </c>
       <c r="N537" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O537" t="inlineStr">
@@ -40239,7 +40239,7 @@
       </c>
       <c r="N540" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O540" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="N541" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O541" t="inlineStr">
@@ -40389,7 +40389,7 @@
       </c>
       <c r="N542" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O542" t="inlineStr">
@@ -40464,7 +40464,7 @@
       </c>
       <c r="N543" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O543" t="inlineStr">
@@ -40539,7 +40539,7 @@
       </c>
       <c r="N544" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O544" t="inlineStr">
@@ -40614,7 +40614,7 @@
       </c>
       <c r="N545" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O545" t="inlineStr">
@@ -40689,7 +40689,7 @@
       </c>
       <c r="N546" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O546" t="inlineStr">
@@ -40764,7 +40764,7 @@
       </c>
       <c r="N547" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O547" t="inlineStr">
@@ -40914,7 +40914,7 @@
       </c>
       <c r="N549" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O549" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="N550" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O550" t="inlineStr">
@@ -41064,7 +41064,7 @@
       </c>
       <c r="N551" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O551" t="inlineStr">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="N552" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O552" t="inlineStr">
@@ -41276,7 +41276,7 @@
       </c>
       <c r="N554" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O554" t="inlineStr">
@@ -41351,7 +41351,7 @@
       </c>
       <c r="N555" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O555" t="inlineStr">
@@ -41426,7 +41426,7 @@
       </c>
       <c r="N556" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O556" t="inlineStr">
@@ -41501,7 +41501,7 @@
       </c>
       <c r="N557" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O557" t="inlineStr">
@@ -41651,7 +41651,7 @@
       </c>
       <c r="N559" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O559" t="inlineStr">
@@ -41726,7 +41726,7 @@
       </c>
       <c r="N560" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O560" t="inlineStr">
@@ -41801,7 +41801,7 @@
       </c>
       <c r="N561" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O561" t="inlineStr">
@@ -42013,7 +42013,7 @@
       </c>
       <c r="N564" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O564" t="inlineStr">
@@ -42088,7 +42088,7 @@
       </c>
       <c r="N565" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O565" t="inlineStr">
@@ -42163,7 +42163,7 @@
       </c>
       <c r="N566" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O566" t="inlineStr">
@@ -42238,7 +42238,7 @@
       </c>
       <c r="N567" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O567" t="inlineStr">
@@ -42388,7 +42388,7 @@
       </c>
       <c r="N569" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O569" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="N570" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O570" t="inlineStr">
@@ -42613,7 +42613,7 @@
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O572" t="inlineStr">
@@ -42688,7 +42688,7 @@
       </c>
       <c r="N573" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O573" t="inlineStr">
@@ -42763,7 +42763,7 @@
       </c>
       <c r="N574" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O574" t="inlineStr">
@@ -42838,7 +42838,7 @@
       </c>
       <c r="N575" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O575" t="inlineStr">
@@ -42913,7 +42913,7 @@
       </c>
       <c r="N576" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O576" t="inlineStr">
@@ -43050,7 +43050,7 @@
       </c>
       <c r="N578" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O578" t="inlineStr">
@@ -43125,7 +43125,7 @@
       </c>
       <c r="N579" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O579" t="inlineStr">
@@ -43200,7 +43200,7 @@
       </c>
       <c r="N580" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O580" t="inlineStr">
@@ -43275,7 +43275,7 @@
       </c>
       <c r="N581" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O581" t="inlineStr">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="N582" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O582" t="inlineStr">
@@ -43425,7 +43425,7 @@
       </c>
       <c r="N583" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O583" t="inlineStr">
@@ -43500,7 +43500,7 @@
       </c>
       <c r="N584" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O584" t="inlineStr">
@@ -43575,7 +43575,7 @@
       </c>
       <c r="N585" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O585" t="inlineStr">
@@ -43650,7 +43650,7 @@
       </c>
       <c r="N586" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O586" t="inlineStr">
@@ -45049,7 +45049,7 @@
       </c>
       <c r="N605" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O605" t="inlineStr">
@@ -45124,7 +45124,7 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
@@ -45199,7 +45199,7 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
@@ -45274,7 +45274,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -45411,7 +45411,7 @@
       </c>
       <c r="N610" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O610" t="inlineStr">
@@ -45486,7 +45486,7 @@
       </c>
       <c r="N611" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O611" t="inlineStr">
@@ -45561,7 +45561,7 @@
       </c>
       <c r="N612" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O612" t="inlineStr">
@@ -45636,7 +45636,7 @@
       </c>
       <c r="N613" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O613" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="N614" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O614" t="inlineStr">
@@ -45786,7 +45786,7 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
@@ -45861,7 +45861,7 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
@@ -45936,7 +45936,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -46073,7 +46073,7 @@
       </c>
       <c r="N619" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O619" t="inlineStr">
@@ -46223,7 +46223,7 @@
       </c>
       <c r="N621" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O621" t="inlineStr">
@@ -46298,7 +46298,7 @@
       </c>
       <c r="N622" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O622" t="inlineStr">
@@ -46373,7 +46373,7 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
@@ -46448,7 +46448,7 @@
       </c>
       <c r="N624" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O624" t="inlineStr">
@@ -46476,20 +46476,20 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>1505887</v>
+        <v>1505888</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Namaha</t>
+          <t>Anurag Kumar</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D625" t="n">
-        <v>16214</v>
+        <v>16208</v>
       </c>
       <c r="E625" t="n">
         <v>48</v>
@@ -46513,17 +46513,17 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Namaha</t>
+          <t>Anurag Kumar</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>NCP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N625" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O625" t="inlineStr">
@@ -46532,7 +46532,7 @@
         </is>
       </c>
       <c r="P625" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q625" t="b">
         <v>0</v>
@@ -46551,20 +46551,20 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>1505888</v>
+        <v>1505887</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Anurag Kumar</t>
+          <t>Namaha</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="D626" t="n">
-        <v>16208</v>
+        <v>16214</v>
       </c>
       <c r="E626" t="n">
         <v>48</v>
@@ -46588,17 +46588,17 @@
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>Anurag Kumar</t>
+          <t>Namaha</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NCP</t>
         </is>
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O626" t="inlineStr">
@@ -46607,7 +46607,7 @@
         </is>
       </c>
       <c r="P626" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q626" t="b">
         <v>0</v>
@@ -46748,7 +46748,7 @@
       </c>
       <c r="N628" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O628" t="inlineStr">
@@ -46823,7 +46823,7 @@
       </c>
       <c r="N629" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O629" t="inlineStr">
@@ -46898,7 +46898,7 @@
       </c>
       <c r="N630" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O630" t="inlineStr">
@@ -46973,7 +46973,7 @@
       </c>
       <c r="N631" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O631" t="inlineStr">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="N632" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O632" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
@@ -47260,7 +47260,7 @@
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="N636" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O636" t="inlineStr">
@@ -47485,7 +47485,7 @@
       </c>
       <c r="N638" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O638" t="inlineStr">
@@ -47513,20 +47513,20 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>1505901</v>
+        <v>1505902</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Deepak Kumar</t>
+          <t>Neelam Singh</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>BHRTAJAP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D639" t="n">
-        <v>16531</v>
+        <v>16397</v>
       </c>
       <c r="E639" t="n">
         <v>49</v>
@@ -47550,17 +47550,17 @@
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>Deepak Kumar</t>
+          <t>Neelam Singh</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
         <is>
-          <t>BHRTAJAP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="N639" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O639" t="inlineStr">
@@ -47569,7 +47569,7 @@
         </is>
       </c>
       <c r="P639" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Q639" t="b">
         <v>0</v>
@@ -47588,20 +47588,20 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>1505902</v>
+        <v>1505901</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Neelam Singh</t>
+          <t>Deepak Kumar</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>BHRTAJAP</t>
         </is>
       </c>
       <c r="D640" t="n">
-        <v>16397</v>
+        <v>16531</v>
       </c>
       <c r="E640" t="n">
         <v>49</v>
@@ -47625,17 +47625,17 @@
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>Neelam Singh</t>
+          <t>Deepak Kumar</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>BHRTAJAP</t>
         </is>
       </c>
       <c r="N640" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="O640" t="inlineStr">
@@ -47644,7 +47644,7 @@
         </is>
       </c>
       <c r="P640" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Q640" t="b">
         <v>0</v>
@@ -47710,7 +47710,7 @@
       </c>
       <c r="N641" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O641" t="inlineStr">
@@ -47785,7 +47785,7 @@
       </c>
       <c r="N642" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O642" t="inlineStr">
@@ -47860,7 +47860,7 @@
       </c>
       <c r="N643" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O643" t="inlineStr">
@@ -47935,7 +47935,7 @@
       </c>
       <c r="N644" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O644" t="inlineStr">
@@ -48147,7 +48147,7 @@
       </c>
       <c r="N647" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O647" t="inlineStr">
@@ -48222,7 +48222,7 @@
       </c>
       <c r="N648" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O648" t="inlineStr">
@@ -48297,7 +48297,7 @@
       </c>
       <c r="N649" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O649" t="inlineStr">
@@ -48372,7 +48372,7 @@
       </c>
       <c r="N650" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O650" t="inlineStr">
@@ -48447,7 +48447,7 @@
       </c>
       <c r="N651" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O651" t="inlineStr">
@@ -48522,7 +48522,7 @@
       </c>
       <c r="N652" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O652" t="inlineStr">
@@ -48734,7 +48734,7 @@
       </c>
       <c r="N655" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O655" t="inlineStr">
@@ -48809,7 +48809,7 @@
       </c>
       <c r="N656" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O656" t="inlineStr">
@@ -48884,7 +48884,7 @@
       </c>
       <c r="N657" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O657" t="inlineStr">
@@ -48959,7 +48959,7 @@
       </c>
       <c r="N658" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O658" t="inlineStr">
@@ -49034,7 +49034,7 @@
       </c>
       <c r="N659" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O659" t="inlineStr">
@@ -49184,7 +49184,7 @@
       </c>
       <c r="N661" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O661" t="inlineStr">
@@ -49321,7 +49321,7 @@
       </c>
       <c r="N663" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O663" t="inlineStr">
@@ -49471,7 +49471,7 @@
       </c>
       <c r="N665" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O665" t="inlineStr">
@@ -49546,7 +49546,7 @@
       </c>
       <c r="N666" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O666" t="inlineStr">
@@ -49621,7 +49621,7 @@
       </c>
       <c r="N667" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O667" t="inlineStr">
@@ -50583,7 +50583,7 @@
       </c>
       <c r="N680" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O680" t="inlineStr">
@@ -50658,7 +50658,7 @@
       </c>
       <c r="N681" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O681" t="inlineStr">
@@ -50733,7 +50733,7 @@
       </c>
       <c r="N682" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O682" t="inlineStr">
@@ -50808,7 +50808,7 @@
       </c>
       <c r="N683" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O683" t="inlineStr">
@@ -50945,7 +50945,7 @@
       </c>
       <c r="N685" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O685" t="inlineStr">
@@ -51020,7 +51020,7 @@
       </c>
       <c r="N686" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O686" t="inlineStr">
@@ -51095,7 +51095,7 @@
       </c>
       <c r="N687" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O687" t="inlineStr">
@@ -51245,7 +51245,7 @@
       </c>
       <c r="N689" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O689" t="inlineStr">
@@ -51320,7 +51320,7 @@
       </c>
       <c r="N690" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O690" t="inlineStr">
@@ -51395,7 +51395,7 @@
       </c>
       <c r="N691" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O691" t="inlineStr">
@@ -51470,7 +51470,7 @@
       </c>
       <c r="N692" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O692" t="inlineStr">
@@ -51545,7 +51545,7 @@
       </c>
       <c r="N693" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O693" t="inlineStr">
@@ -51695,7 +51695,7 @@
       </c>
       <c r="N695" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O695" t="inlineStr">
@@ -51770,7 +51770,7 @@
       </c>
       <c r="N696" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O696" t="inlineStr">
@@ -51845,7 +51845,7 @@
       </c>
       <c r="N697" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O697" t="inlineStr">
@@ -51920,7 +51920,7 @@
       </c>
       <c r="N698" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O698" t="inlineStr">
@@ -52132,7 +52132,7 @@
       </c>
       <c r="N701" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O701" t="inlineStr">
@@ -52207,7 +52207,7 @@
       </c>
       <c r="N702" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O702" t="inlineStr">
@@ -52282,7 +52282,7 @@
       </c>
       <c r="N703" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O703" t="inlineStr">
@@ -52357,7 +52357,7 @@
       </c>
       <c r="N704" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O704" t="inlineStr">
@@ -52432,7 +52432,7 @@
       </c>
       <c r="N705" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O705" t="inlineStr">
@@ -52507,7 +52507,7 @@
       </c>
       <c r="N706" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O706" t="inlineStr">
@@ -52582,7 +52582,7 @@
       </c>
       <c r="N707" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O707" t="inlineStr">
@@ -52657,7 +52657,7 @@
       </c>
       <c r="N708" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O708" t="inlineStr">
@@ -52732,7 +52732,7 @@
       </c>
       <c r="N709" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O709" t="inlineStr">
@@ -52807,7 +52807,7 @@
       </c>
       <c r="N710" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O710" t="inlineStr">
@@ -52882,7 +52882,7 @@
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O711" t="inlineStr">
@@ -52957,7 +52957,7 @@
       </c>
       <c r="N712" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O712" t="inlineStr">
@@ -53094,7 +53094,7 @@
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O714" t="inlineStr">
@@ -53169,7 +53169,7 @@
       </c>
       <c r="N715" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O715" t="inlineStr">
@@ -53244,7 +53244,7 @@
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O716" t="inlineStr">
@@ -53319,7 +53319,7 @@
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O717" t="inlineStr">
@@ -53469,7 +53469,7 @@
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O719" t="inlineStr">
@@ -53544,7 +53544,7 @@
       </c>
       <c r="N720" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O720" t="inlineStr">
@@ -53619,7 +53619,7 @@
       </c>
       <c r="N721" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O721" t="inlineStr">
@@ -53694,7 +53694,7 @@
       </c>
       <c r="N722" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O722" t="inlineStr">
@@ -53831,7 +53831,7 @@
       </c>
       <c r="N724" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O724" t="inlineStr">
@@ -53906,7 +53906,7 @@
       </c>
       <c r="N725" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O725" t="inlineStr">
@@ -53981,7 +53981,7 @@
       </c>
       <c r="N726" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O726" t="inlineStr">
@@ -54056,7 +54056,7 @@
       </c>
       <c r="N727" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O727" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="N728" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O728" t="inlineStr">
@@ -55168,7 +55168,7 @@
       </c>
       <c r="N742" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O742" t="inlineStr">
@@ -55243,7 +55243,7 @@
       </c>
       <c r="N743" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O743" t="inlineStr">
@@ -55318,7 +55318,7 @@
       </c>
       <c r="N744" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O744" t="inlineStr">
@@ -55393,7 +55393,7 @@
       </c>
       <c r="N745" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O745" t="inlineStr">
@@ -55605,7 +55605,7 @@
       </c>
       <c r="N748" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O748" t="inlineStr">
@@ -55680,7 +55680,7 @@
       </c>
       <c r="N749" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O749" t="inlineStr">
@@ -55755,7 +55755,7 @@
       </c>
       <c r="N750" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O750" t="inlineStr">
@@ -55905,7 +55905,7 @@
       </c>
       <c r="N752" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O752" t="inlineStr">
@@ -55980,7 +55980,7 @@
       </c>
       <c r="N753" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O753" t="inlineStr">
@@ -56055,7 +56055,7 @@
       </c>
       <c r="N754" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O754" t="inlineStr">
@@ -56130,7 +56130,7 @@
       </c>
       <c r="N755" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O755" t="inlineStr">
@@ -56205,7 +56205,7 @@
       </c>
       <c r="N756" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O756" t="inlineStr">
@@ -56280,7 +56280,7 @@
       </c>
       <c r="N757" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O757" t="inlineStr">
@@ -56355,7 +56355,7 @@
       </c>
       <c r="N758" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O758" t="inlineStr">
@@ -56430,7 +56430,7 @@
       </c>
       <c r="N759" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O759" t="inlineStr">
@@ -56567,7 +56567,7 @@
       </c>
       <c r="N761" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O761" t="inlineStr">
@@ -56642,7 +56642,7 @@
       </c>
       <c r="N762" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O762" t="inlineStr">
@@ -56792,7 +56792,7 @@
       </c>
       <c r="N764" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O764" t="inlineStr">
@@ -56867,7 +56867,7 @@
       </c>
       <c r="N765" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O765" t="inlineStr">
@@ -56942,7 +56942,7 @@
       </c>
       <c r="N766" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O766" t="inlineStr">
@@ -57092,7 +57092,7 @@
       </c>
       <c r="N768" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O768" t="inlineStr">
@@ -57167,7 +57167,7 @@
       </c>
       <c r="N769" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O769" t="inlineStr">
@@ -57242,7 +57242,7 @@
       </c>
       <c r="N770" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="O770" t="inlineStr">
